--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B342A8C3-5C4D-44F5-BCE6-C49990D100F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6ED62A-E3C0-46E4-B432-2FCFB11CBCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>NONE</t>
   </si>
@@ -38,14 +38,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GROUP_DISABLED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GROUP_TARGET_DISABLED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BIRTHDAY_NOT_MATCHED</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,6 +63,26 @@
   </si>
   <si>
     <t>NOT_FOUND_CHARACTER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FOUND_OPTION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DISABLED_WHISPER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DISABLED_GROUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DISABLED_GROUP_TARGET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DISABLED_WHISPER_TARGET</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -469,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -486,7 +498,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -510,7 +522,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -518,7 +530,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
@@ -526,7 +538,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
@@ -534,7 +546,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
@@ -542,7 +554,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
@@ -550,7 +562,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
@@ -558,7 +570,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
@@ -566,10 +578,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6ED62A-E3C0-46E4-B432-2FCFB11CBCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97294240-5133-4812-B4E6-13F92C8DAE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>NONE</t>
   </si>
@@ -83,6 +83,10 @@
   </si>
   <si>
     <t>DISABLED_WHISPER_TARGET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DISTRIBUTED_LOCK_FAILED</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -481,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -608,6 +612,14 @@
         <v>14</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97294240-5133-4812-B4E6-13F92C8DAE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2065B309-B6BC-49D2-86C3-6DF8673F9AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>NONE</t>
   </si>
@@ -87,6 +87,22 @@
   </si>
   <si>
     <t>DISTRIBUTED_LOCK_FAILED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROUP_NOT_JOINED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROUP_NOT_FOUND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CANNOT_GROUP_SELF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FOUND_MAP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -620,6 +636,38 @@
         <v>15</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2065B309-B6BC-49D2-86C3-6DF8673F9AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F86D6B8-9E82-49BC-B48C-89054FF7742F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>NONE</t>
   </si>
@@ -103,6 +103,10 @@
   </si>
   <si>
     <t>NOT_FOUND_MAP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_GROUP_MASTER</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -501,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -668,6 +672,14 @@
         <v>19</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F86D6B8-9E82-49BC-B48C-89054FF7742F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7040A5-B5FB-4F02-8F54-E4798330500F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>NONE</t>
   </si>
@@ -107,6 +107,10 @@
   </si>
   <si>
     <t>NOT_GROUP_MASTER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARTICLE_NOT_EXISTS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -505,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -680,6 +684,14 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7040A5-B5FB-4F02-8F54-E4798330500F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335ED13A-4E7B-47A7-B1B0-D5CDB182B4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>NONE</t>
   </si>
@@ -111,6 +111,37 @@
   </si>
   <si>
     <t>ARTICLE_NOT_EXISTS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_NAME_ALREADY_EXISTS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_ALREADY_JOINED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_NOT_JOINED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FOUND_CLAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_MEMBER_EXISTS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_NO_PRIVILEGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FOUND_CLAN_MEMBER</t>
+  </si>
+  <si>
+    <t>CLAN_NOT_MATCHED</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -509,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -692,6 +723,70 @@
         <v>21</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335ED13A-4E7B-47A7-B1B0-D5CDB182B4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785B3E55-E30C-4FD7-831E-A3BACF95F98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>NONE</t>
   </si>
@@ -142,6 +142,14 @@
   </si>
   <si>
     <t>CLAN_NOT_MATCHED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FOUND_CHARACTER_SYNC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_CANNOT_LEAVEE_MASTER</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -540,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -787,6 +795,22 @@
         <v>29</v>
       </c>
     </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785B3E55-E30C-4FD7-831E-A3BACF95F98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE99FD4-5A96-4CCE-8167-702C30AD450F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>NONE</t>
   </si>
@@ -150,6 +150,14 @@
   </si>
   <si>
     <t>CLAN_CANNOT_LEAVEE_MASTER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_TITLE_NOT_CHANGED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAN_TITLE_TOO_SHORT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -548,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -811,6 +819,22 @@
         <v>31</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE99FD4-5A96-4CCE-8167-702C30AD450F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAAA745-6176-47D5-890C-FDB0D37409B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>NONE</t>
   </si>
@@ -158,6 +158,14 @@
   </si>
   <si>
     <t>CLAN_TITLE_TOO_SHORT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAIL_NOT_EXISTS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FOUND_MAIL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -556,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
@@ -835,6 +843,22 @@
         <v>33</v>
       </c>
     </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAAA745-6176-47D5-890C-FDB0D37409B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41A441B-F36A-4A47-A929-AC6E1F52555D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>NONE</t>
   </si>
@@ -166,6 +166,18 @@
   </si>
   <si>
     <t>NOT_FOUND_MAIL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVALID_CLAN_POSITION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CANNOT_KICK_SELF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CANNOT_CHANGE_CLAN_POSITION_SELF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -232,7 +244,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -564,10 +576,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -859,6 +871,30 @@
         <v>35</v>
       </c>
     </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41A441B-F36A-4A47-A929-AC6E1F52555D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3F366B-DFF6-4767-8809-B70FD178D41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>NONE</t>
   </si>
@@ -169,15 +169,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>INVALID_CLAN_POSITION</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CANNOT_KICK_SELF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CANNOT_CHANGE_CLAN_POSITION_SELF</t>
+    <t>CANNOT_INVITE_SELF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CANNOT_CHANGE_CLAN_ROLE_SELF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVALID_CLAN_ROLE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -873,7 +877,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1">
         <v>36</v>
@@ -881,7 +885,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1">
         <v>37</v>
@@ -893,6 +897,14 @@
       </c>
       <c r="B39" s="1">
         <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="1">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3F366B-DFF6-4767-8809-B70FD178D41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE6426E-EAD3-4FAD-9060-17F1FC895983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>NONE</t>
   </si>
@@ -182,6 +182,13 @@
   </si>
   <si>
     <t>INVALID_CLAN_ROLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FOUND_BAN</t>
+  </si>
+  <si>
+    <t>BANNED</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -248,7 +255,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -580,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -907,6 +914,22 @@
         <v>39</v>
       </c>
     </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE6426E-EAD3-4FAD-9060-17F1FC895983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4238D5-6B93-4DA2-AADC-3EEEB0F53FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>NONE</t>
   </si>
@@ -190,6 +190,39 @@
   <si>
     <t>BANNED</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MARKETPLACE_LISTING_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_LISTING_EXPIRED</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_NOT_LISTING_OWNER</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_LISTING_ALREADY_SOLD</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_LISTING_ALREADY_CANCELLED</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_INSUFFICIENT_FUNDS</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_INVALID_PRICE</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_INVALID_EXPIRE_HOURS</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_ITEM_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_PENDING_TRANSACTION_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_PENDING_RETURN_NOT_FOUND</t>
   </si>
 </sst>
 </file>
@@ -255,7 +288,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -587,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -930,6 +963,94 @@
         <v>41</v>
       </c>
     </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4238D5-6B93-4DA2-AADC-3EEEB0F53FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C568C3-CAFC-4FB0-8F0B-46F0552C3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>NONE</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>MARKETPLACE_PENDING_RETURN_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_INVALID_PAGE_NUMBER</t>
   </si>
 </sst>
 </file>
@@ -620,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -1051,6 +1054,14 @@
         <v>52</v>
       </c>
     </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C568C3-CAFC-4FB0-8F0B-46F0552C3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCE48B7-BF3D-4579-9EDA-61201796E1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>NONE</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>MARKETPLACE_INVALID_PAGE_NUMBER</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_ID_ALREADY_EXISTS</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_INSUFFICIENT_STOCK</t>
   </si>
 </sst>
 </file>
@@ -291,7 +297,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -623,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -1062,6 +1068,22 @@
         <v>53</v>
       </c>
     </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCE48B7-BF3D-4579-9EDA-61201796E1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B1CA88-5A7D-4D90-8C04-5F929F394142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>NONE</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>MARKETPLACE_INSUFFICIENT_STOCK</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_LISTING_LIMIT_EXCEEDED</t>
   </si>
 </sst>
 </file>
@@ -297,7 +300,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -629,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -1084,6 +1087,14 @@
         <v>55</v>
       </c>
     </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B1CA88-5A7D-4D90-8C04-5F929F394142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A9A627-886B-46CF-ACEF-D08786217889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>NONE</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>MARKETPLACE_LISTING_LIMIT_EXCEEDED</t>
+  </si>
+  <si>
+    <t>MAINTENANCE</t>
   </si>
 </sst>
 </file>
@@ -632,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -1095,6 +1098,14 @@
         <v>56</v>
       </c>
     </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A9A627-886B-46CF-ACEF-D08786217889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA6A988-08BA-4F63-9FFD-3A21FB750A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>NONE</t>
   </si>
@@ -238,6 +238,10 @@
   </si>
   <si>
     <t>MAINTENANCE</t>
+  </si>
+  <si>
+    <t>MARKETPLACE_ITEM_NOT_TRADEABLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -303,7 +307,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -635,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -1106,6 +1110,14 @@
         <v>57</v>
       </c>
     </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA6A988-08BA-4F63-9FFD-3A21FB750A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AC18A7-BEC5-4510-805E-BD18998A330E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ERROR_CODE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>NONE</t>
   </si>
@@ -242,6 +242,36 @@
   <si>
     <t>MARKETPLACE_ITEM_NOT_TRADEABLE</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATCHMAKING_UNKNOWN_QUEUE</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_ALREADY_ENROLLED</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_DUPLICATE_ENTRY</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_REGISTRY_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_NOT_PARTICIPANT</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_MATCH_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_ALREADY_CONFIRMED</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_ALREADY_DECLINED</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_CONFIRM_EXPIRED</t>
+  </si>
+  <si>
+    <t>MATCHMAKING_NOT_IN_WAITING_STATE</t>
   </si>
 </sst>
 </file>
@@ -639,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" style="1" bestFit="1" customWidth="1"/>
@@ -1118,6 +1148,86 @@
         <v>58</v>
       </c>
     </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
